--- a/data.xlsx
+++ b/data.xlsx
@@ -498,7 +498,7 @@
         <v>ebouwbcw</v>
       </c>
       <c r="E6" t="str">
-        <v>Soman</v>
+        <v>aeroplane</v>
       </c>
     </row>
     <row r="7">
@@ -532,7 +532,7 @@
         <v>bouhfiqjqjd ne. r.  t</v>
       </c>
       <c r="E8" t="str">
-        <v>Sameer</v>
+        <v>jet</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -447,7 +447,7 @@
         <v xml:space="preserve">hwiebfuw hwebcw </v>
       </c>
       <c r="E3" t="str">
-        <v>Dg</v>
+        <v>Dog</v>
       </c>
     </row>
     <row r="4">

--- a/data.xlsx
+++ b/data.xlsx
@@ -515,7 +515,7 @@
         <v>ouehouf</v>
       </c>
       <c r="E7" t="str">
-        <v>Fan</v>
+        <v>Fangs</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -532,7 +532,7 @@
         <v>bouhfiqjqjd ne. r.  t</v>
       </c>
       <c r="E8" t="str">
-        <v>jet</v>
+        <v>jetski</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -481,7 +481,7 @@
         <v>bewubu</v>
       </c>
       <c r="E5" t="str">
-        <v>tree</v>
+        <v>Horse</v>
       </c>
     </row>
     <row r="6">

--- a/data.xlsx
+++ b/data.xlsx
@@ -464,7 +464,7 @@
         <v xml:space="preserve">bjbob hdi hpih </v>
       </c>
       <c r="E4" t="str">
-        <v>Cat</v>
+        <v>Tortoise</v>
       </c>
     </row>
     <row r="5">

--- a/data.xlsx
+++ b/data.xlsx
@@ -447,7 +447,7 @@
         <v xml:space="preserve">hwiebfuw hwebcw </v>
       </c>
       <c r="E3" t="str">
-        <v>Dog</v>
+        <v>ppp</v>
       </c>
     </row>
     <row r="4">
